--- a/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
+++ b/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,126 +479,6 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>ITID3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sistemiDiMisura</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Serpelloni</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ITID3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>robotica</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tampalini</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ITID3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cybersecurity</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Gringoli</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ITID3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>elettronicaGenerale</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Flammini</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Informatica3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sistemiOperativi</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Baroni</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Informatica3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LaboratorioRasperry</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sisinni</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Informatica3</t>
         </is>
       </c>
     </row>
@@ -613,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD9"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,1038 +1119,6 @@
         <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bau</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Serpelloni</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tampalini</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gringoli</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flammini</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Baroni</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2285,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2573,41 +1421,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -2739,522 +1587,6 @@
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B31</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CaNoa</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3269,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,178 +2055,6 @@
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Informatica3</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
+++ b/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="corsi" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="88">
   <si>
     <t xml:space="preserve">corso</t>
   </si>
@@ -53,6 +53,48 @@
     <t xml:space="preserve">Kovarik</t>
   </si>
   <si>
+    <t xml:space="preserve">sistemiDiMisura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serpelloni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robotica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampalini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gringoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elettronicaGenerale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flammini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informatica3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sistemiOperativi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baroni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaboratorioRasperry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BasiDati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rula</t>
+  </si>
+  <si>
     <t xml:space="preserve">mon08</t>
   </si>
   <si>
@@ -218,10 +260,22 @@
     <t xml:space="preserve">fri18</t>
   </si>
   <si>
+    <t xml:space="preserve">Bau</t>
+  </si>
+  <si>
     <t xml:space="preserve">aula</t>
   </si>
   <si>
     <t xml:space="preserve">N6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaNoa</t>
   </si>
   <si>
     <t xml:space="preserve">gruppiStudenti</t>
@@ -314,7 +368,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -510,8 +564,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="11.53"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -532,7 +590,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -553,6 +611,104 @@
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +727,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -579,169 +735,169 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,6 +1237,1196 @@
         <v>1</v>
       </c>
       <c r="BD3" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1100,182 +2446,182 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="AR1" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -1440,6 +2786,516 @@
         <v>1</v>
       </c>
       <c r="BD2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1459,177 +3315,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="AT1" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1799,6 +3655,176 @@
         <v>1</v>
       </c>
       <c r="BD2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1823,17 +3849,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>12</v>

--- a/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
+++ b/application/V5/problemGeneratorDiego/timetablingTemplateDiego.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="corsi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàProfessori" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàAule" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="disponibilitàGruppiStudenti" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="configurazione" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="corsi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="disponibilitàProfessori" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="disponibilitàAule" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="disponibilitàGruppiStudenti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="configurazione" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,28 +429,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>corso</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ore settimanali</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>professore</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>gruppoStudenti</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Corso</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ore Settimanali</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Professore</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GruppoStudenti</t>
         </is>
       </c>
     </row>
@@ -525,38 +537,98 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elettronicaGenerale</t>
+          <t>cybersecurity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Flammini</t>
+          <t>Gringoli</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Informatica3</t>
+          <t>ITID3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>elettronicaGenerale</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Flammini</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>sistemiOperativi</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>5</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Baroni</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LaboratorioRasperry</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sisinni</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Informatica3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BasiDati</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Informatica3</t>
         </is>
@@ -573,286 +645,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD8"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>professore</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Professore</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mon08</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mon09</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mon10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mon11</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mon12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mon13</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mon14</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mon15</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mon16</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mon17</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mon18</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tue08</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tue09</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>tue10</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tue11</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>tue12</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>tue13</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>tue14</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>tue15</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>tue16</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tue17</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tue18</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>wed08</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>wed09</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>wed10</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>wed11</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>wed12</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>wed13</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>wed14</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>wed15</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>wed16</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>wed17</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>wed18</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>thu08</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>thu09</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>thu10</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>thu11</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>thu12</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>thu13</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>thu14</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>thu15</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>thu16</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>thu17</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>thu18</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fri08</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>fri09</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fri10</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fri11</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fri12</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fri13</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fri14</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>fri15</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>fri16</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>fri17</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>fri18</t>
         </is>
@@ -1721,7 +1793,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Flammini</t>
+          <t>Gringoli</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1893,172 +1965,516 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Flammini</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Baroni</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2073,286 +2489,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>aula</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Aula</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mon08</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mon09</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mon10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mon11</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mon12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mon13</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mon14</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mon15</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mon16</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mon17</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mon18</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tue08</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tue09</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>tue10</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tue11</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>tue12</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>tue13</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>tue14</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>tue15</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>tue16</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tue17</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tue18</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>wed08</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>wed09</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>wed10</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>wed11</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>wed12</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>wed13</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>wed14</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>wed15</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>wed16</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>wed17</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>wed18</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>thu08</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>thu09</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>thu10</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>thu11</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>thu12</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>thu13</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>thu14</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>thu15</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>thu16</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>thu17</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>thu18</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fri08</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>fri09</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fri10</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fri11</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fri12</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fri13</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fri14</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>fri15</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>fri16</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>fri17</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>fri18</t>
         </is>
@@ -2871,6 +3287,178 @@
         <v>1</v>
       </c>
       <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CaNoa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2889,282 +3477,282 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>gruppiStudenti</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GruppiStudenti</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>mon08</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mon09</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mon10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mon11</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mon12</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mon13</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mon14</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mon15</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mon16</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mon17</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mon18</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tue08</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tue09</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>tue10</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tue11</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>tue12</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>tue13</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>tue14</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>tue15</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>tue16</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>tue17</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tue18</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>wed08</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>wed09</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>wed10</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>wed11</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>wed12</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>wed13</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>wed14</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>wed15</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>wed16</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>wed17</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>wed18</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>thu08</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>thu09</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>thu10</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>thu11</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>thu12</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>thu13</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>thu14</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>thu15</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>thu16</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>thu17</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>thu18</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fri08</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>fri09</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fri10</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fri11</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fri12</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fri13</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fri14</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>fri15</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>fri16</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>fri17</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>fri18</t>
         </is>
@@ -3529,25 +4117,25 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>configurazioni</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>valori</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Configurazione</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valore</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ora pausa pranzo</t>
+          <t>Ora Pausa Pranzo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
